--- a/outputs/submission_tables_xlsx/Supplementary Table 12.xlsx
+++ b/outputs/submission_tables_xlsx/Supplementary Table 12.xlsx
@@ -343,227 +343,693 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Primary DALY series</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Income group</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>DALYs</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Total DALYs in income group</t>
+          <t>Model role</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Percentage of income-group DALYs (%)</t>
+          <t>Ljung-Box p value</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Total DALYs among all 128 LMICs</t>
+          <t>Residual autocorrelation detected at the 5% level</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Percentage of total DALYs among all 128 LMICs (%)</t>
+          <t>Eligible under the prespecified rule</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MAPE (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Empirical coverage of the nominal 95% range (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Rank by MAPE among all four candidates</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Selected</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Low income</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>40230.11682819844</v>
-      </c>
-      <c r="D2">
-        <v>210793.0887006726</v>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
       </c>
       <c r="E2">
-        <v>19.085121374793</v>
-      </c>
-      <c r="F2">
-        <v>6560540.221705612</v>
-      </c>
-      <c r="G2">
-        <v>0.6132134773764012</v>
+        <v>0.9130518874851072</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2">
+        <v>4.236084851669204</v>
+      </c>
+      <c r="I2">
+        <v>2.565690293850184</v>
+      </c>
+      <c r="J2">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>23921.96771165704</v>
-      </c>
-      <c r="D3">
-        <v>4882247.541198344</v>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
       </c>
       <c r="E3">
-        <v>0.4899785910033028</v>
-      </c>
-      <c r="F3">
-        <v>6560540.221705612</v>
-      </c>
-      <c r="G3">
-        <v>0.3646341140095594</v>
+        <v>0.5592691983726177</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3">
+        <v>4.932336441461872</v>
+      </c>
+      <c r="I3">
+        <v>2.982226585939642</v>
+      </c>
+      <c r="J3">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Syrian Arab Republic</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Low income</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>12617.95167722327</v>
-      </c>
-      <c r="D4">
-        <v>210793.0887006726</v>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
       </c>
       <c r="E4">
-        <v>5.985941832818262</v>
-      </c>
-      <c r="F4">
-        <v>6560540.221705612</v>
-      </c>
-      <c r="G4">
-        <v>0.1923309857239598</v>
+        <v>6.294964549624639e-14</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4">
+        <v>11.86681736057764</v>
+      </c>
+      <c r="I4">
+        <v>7.016938868474196</v>
+      </c>
+      <c r="J4">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Low income</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Low income</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>8490.565633409135</v>
-      </c>
-      <c r="D5">
-        <v>210793.0887006726</v>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
       </c>
       <c r="E5">
-        <v>4.027914617953052</v>
-      </c>
-      <c r="F5">
-        <v>6560540.221705612</v>
-      </c>
-      <c r="G5">
-        <v>0.1294186964256086</v>
+        <v>2.531308496145357e-13</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>17.2833233112116</v>
+      </c>
+      <c r="I5">
+        <v>10.18156696114595</v>
+      </c>
+      <c r="J5">
+        <v>4.347826086956522</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Low income</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>2458.036285744085</v>
-      </c>
-      <c r="D6">
-        <v>210793.0887006726</v>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
       </c>
       <c r="E6">
-        <v>1.166089600420681</v>
-      </c>
-      <c r="F6">
-        <v>6560540.221705612</v>
-      </c>
-      <c r="G6">
-        <v>0.03746697989308331</v>
+        <v>0.5923091166627176</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6">
+        <v>4.189659760031997</v>
+      </c>
+      <c r="I6">
+        <v>2.047986567518579</v>
+      </c>
+      <c r="J6">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Low income</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>4166.713375749698</v>
-      </c>
-      <c r="D7">
-        <v>210793.0887006726</v>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
       </c>
       <c r="E7">
-        <v>1.976684056120291</v>
-      </c>
-      <c r="F7">
-        <v>6560540.221705612</v>
-      </c>
-      <c r="G7">
-        <v>0.06351174194411742</v>
+        <v>0.4393304937376168</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7">
+        <v>4.494409787145069</v>
+      </c>
+      <c r="I7">
+        <v>2.213826009531883</v>
+      </c>
+      <c r="J7">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>All six excluded countries</t>
+          <t>Lower middle income</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Combined</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>91885.35151198164</v>
-      </c>
-      <c r="F8">
-        <v>6560540.221705612</v>
-      </c>
-      <c r="G8">
-        <v>1.400575995372729</v>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>1.155699071997418e-07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8">
+        <v>8.633029768854529</v>
+      </c>
+      <c r="I8">
+        <v>4.261724816585298</v>
+      </c>
+      <c r="J8">
+        <v>15.94202898550724</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>3.548123614915966e-07</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9">
+        <v>15.42269152486982</v>
+      </c>
+      <c r="I9">
+        <v>7.5081016281795</v>
+      </c>
+      <c r="J9">
+        <v>14.49275362318841</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>0.01626805210156146</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10">
+        <v>3.876429794817598</v>
+      </c>
+      <c r="I10">
+        <v>2.305066947645936</v>
+      </c>
+      <c r="J10">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>0.2882447320013748</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11">
+        <v>4.10718713917293</v>
+      </c>
+      <c r="I11">
+        <v>2.433929380334716</v>
+      </c>
+      <c r="J11">
+        <v>40.57971014492754</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>0.001138745732546686</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12">
+        <v>4.967917704575404</v>
+      </c>
+      <c r="I12">
+        <v>2.922356768442076</v>
+      </c>
+      <c r="J12">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DALY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Naive</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>0.03079229095084301</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13">
+        <v>8.842480813590777</v>
+      </c>
+      <c r="I13">
+        <v>5.182835218379067</v>
+      </c>
+      <c r="J13">
+        <v>37.68115942028986</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
   </sheetData>
